--- a/Result/profitability/4609.xlsx
+++ b/Result/profitability/4609.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0625</v>
+        <v>-0.06749999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>17.435</v>
+        <v>16.5475</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.73</v>
       </c>
       <c r="M3" t="n">
-        <v>0.035</v>
+        <v>0.0475</v>
       </c>
       <c r="N3" t="n">
-        <v>16.81875</v>
+        <v>16.73125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.97</v>
       </c>
       <c r="M4" t="n">
-        <v>0.305</v>
+        <v>0.31</v>
       </c>
       <c r="N4" t="n">
-        <v>17.725</v>
+        <v>18.08875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.09</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4575</v>
+        <v>0.4875</v>
       </c>
       <c r="N5" t="n">
-        <v>19.6275</v>
+        <v>17.79</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.36</v>
       </c>
       <c r="M6" t="n">
-        <v>0.54375</v>
+        <v>0.48375</v>
       </c>
       <c r="N6" t="n">
-        <v>18.985</v>
+        <v>15.815</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5575</v>
+        <v>0.55125</v>
       </c>
       <c r="N7" t="n">
-        <v>17.23125</v>
+        <v>18.4125</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.89</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6737500000000001</v>
+        <v>0.6725</v>
       </c>
       <c r="N8" t="n">
-        <v>20.50625</v>
+        <v>22.23</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.14</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7637499999999999</v>
+        <v>0.76375</v>
       </c>
       <c r="N10" t="n">
         <v>23.4925</v>
@@ -1899,7 +1899,7 @@
         <v>0.34</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5762499999999999</v>
+        <v>0.57625</v>
       </c>
       <c r="N12" t="n">
         <v>23.4025</v>
@@ -2026,7 +2026,7 @@
         <v>0.68</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5249999999999999</v>
+        <v>0.525</v>
       </c>
       <c r="N13" t="n">
         <v>22.52</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4609</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>52</v>
+      </c>
+      <c r="D75" t="n">
+        <v>45</v>
+      </c>
+      <c r="E75" t="n">
+        <v>7</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.37</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-19</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-36.19%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>15</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.065</v>
+      </c>
+      <c r="N75" t="n">
+        <v>17.08375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.009999999999999995</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>23.77586206896552</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.7272727272727273</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-14.7</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.5056759545923633</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
